--- a/ZAC_zzx/results/fourway/四方法对比_ga.xlsx
+++ b/ZAC_zzx/results/fourway/四方法对比_ga.xlsx
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ZAC 数据集（hpca 18 电路）　四方法×四指标。保真度=五项模型同判分（0.9997^1q × 0.995^2q × 0.999^(2×人次) × Π(1−idle/T)，同架构 ZAC repro）。move批=搬运班次数（ZAC/遗传=rearrangeJob 条数；ICCAD=load…store 作业数，口径近似，跨方法只作参考）。move时间=纯搬运执行时长，不含门时间（ZAC/遗传=Σ搬送批起止区间；ICCAD=Σ作业 2×15μs+√(d/0.00275)）。编译时间=电脑求出该解的耗时（ZAC/遗传=编译流水线 total；ICCAD=transpile+compile 实测，不含 python 启动）。遗传(前瞻)=γ0=0.5 主配置；遗传(无前瞻)=γ0=0（下次使用锚点项归零，其余设置全同）。ICCAD 配置=astar 优先、超时回落 agnostic。汇总行只统计四法数据齐全的电路（N 见行内标注）。</t>
+          <t>ZAC 数据集（hpca 18 电路）　四方法×四指标。保真度=五项模型同判分（0.9997^1q × 0.995^2q × 0.999^(2×人次) × Π(1−idle/T)，同架构 ZAC repro）。move批=重排步数 Num. Rearr. Steps（ICCAD'25 Table I 口径）：一次完整的 AOD 重排循环计 1 步——ZAC/遗传=rearrangeJob 条数（activate+move+deactivate），ICCAD=load…store 作业数，语义 1:1 对应；qmap 侧计数已对论文 Table I 逐位复现验证（seca 112 步=112、12/15 行精确一致），且全产物 26 万班次零空班（无水分计数）。move时间=纯搬运执行时长，不含门时间（ZAC/遗传=Σ搬送批起止区间；ICCAD=Σ作业 2×15μs+√(d/0.00275)）。编译时间=电脑求出该解的耗时（ZAC/遗传=编译流水线 total；ICCAD=transpile+compile 实测，不含 python 启动）。遗传(前瞻)=γ0=0.5 主配置；遗传(无前瞻)=γ0=0（下次使用锚点项归零，其余设置全同）。ICCAD 配置=astar 优先、超时回落 agnostic。汇总行只统计四法数据齐全的电路（N 见行内标注）。</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>ZAC原始
-move批</t>
+Rearr.Steps</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -506,7 +506,7 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>ICCAD
-move批</t>
+Rearr.Steps</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>遗传(无前瞻)
-move批</t>
+Rearr.Steps</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="P2" s="2" t="inlineStr">
         <is>
           <t>遗传(前瞻)
-move批</t>
+Rearr.Steps</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>move批</t>
+          <t>Rearr.Steps</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>geomean /ZAC：batches</t>
+          <t>geomean /ZAC：Rearr.Steps</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1902,7 +1902,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICCAD 数据集（qmap examples）　四方法×四指标。保真度=五项模型同判分（0.9997^1q × 0.995^2q × 0.999^(2×人次) × Π(1−idle/T)，同架构 ZAC repro）。move批=搬运班次数（ZAC/遗传=rearrangeJob 条数；ICCAD=load…store 作业数，口径近似，跨方法只作参考）。move时间=纯搬运执行时长，不含门时间（ZAC/遗传=Σ搬送批起止区间；ICCAD=Σ作业 2×15μs+√(d/0.00275)）。编译时间=电脑求出该解的耗时（ZAC/遗传=编译流水线 total；ICCAD=transpile+compile 实测，不含 python 启动）。遗传(前瞻)=γ0=0.5 主配置；遗传(无前瞻)=γ0=0（下次使用锚点项归零，其余设置全同）。ICCAD 配置=astar 优先、超时回落 agnostic。汇总行只统计四法数据齐全的电路（N 见行内标注）。</t>
+          <t>ICCAD 数据集（qmap examples）　四方法×四指标。保真度=五项模型同判分（0.9997^1q × 0.995^2q × 0.999^(2×人次) × Π(1−idle/T)，同架构 ZAC repro）。move批=重排步数 Num. Rearr. Steps（ICCAD'25 Table I 口径）：一次完整的 AOD 重排循环计 1 步——ZAC/遗传=rearrangeJob 条数（activate+move+deactivate），ICCAD=load…store 作业数，语义 1:1 对应；qmap 侧计数已对论文 Table I 逐位复现验证（seca 112 步=112、12/15 行精确一致），且全产物 26 万班次零空班（无水分计数）。move时间=纯搬运执行时长，不含门时间（ZAC/遗传=Σ搬送批起止区间；ICCAD=Σ作业 2×15μs+√(d/0.00275)）。编译时间=电脑求出该解的耗时（ZAC/遗传=编译流水线 total；ICCAD=transpile+compile 实测，不含 python 启动）。遗传(前瞻)=γ0=0.5 主配置；遗传(无前瞻)=γ0=0（下次使用锚点项归零，其余设置全同）。ICCAD 配置=astar 优先、超时回落 agnostic。汇总行只统计四法数据齐全的电路（N 见行内标注）。</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>ZAC原始
-move批</t>
+Rearr.Steps</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>ICCAD
-move批</t>
+Rearr.Steps</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>遗传(无前瞻)
-move批</t>
+Rearr.Steps</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       <c r="P2" s="2" t="inlineStr">
         <is>
           <t>遗传(前瞻)
-move批</t>
+Rearr.Steps</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>move批</t>
+          <t>Rearr.Steps</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -9685,7 +9685,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>geomean /ZAC：batches</t>
+          <t>geomean /ZAC：Rearr.Steps</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
